--- a/data/trans_orig/Q24A01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q24A01-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de cigarrillos que fuman al día</t>
+          <t>Número medio de cigarrillos que fuman al día (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,22; 17,13</t>
+          <t>15,25; 17,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 19,37</t>
+          <t>16,62; 19,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,12; 16,41</t>
+          <t>14,16; 16,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,32; 16,18</t>
+          <t>13,3; 16,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,3; 11,31</t>
+          <t>9,26; 11,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,48; 13,05</t>
+          <t>10,46; 12,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,78; 10,98</t>
+          <t>8,77; 11,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 9,74</t>
+          <t>8,19; 9,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,51; 15,15</t>
+          <t>13,5; 15,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,41; 16,61</t>
+          <t>14,58; 16,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 13,99</t>
+          <t>12,16; 13,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,52; 13,43</t>
+          <t>11,4; 13,36</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,69; 18,86</t>
+          <t>16,74; 18,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,97; 17,13</t>
+          <t>14,97; 16,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,63; 14,55</t>
+          <t>12,59; 14,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,69; 15,14</t>
+          <t>12,64; 15,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,93; 13,39</t>
+          <t>10,99; 13,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,17; 12,84</t>
+          <t>11,06; 12,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,89; 11,73</t>
+          <t>9,97; 11,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,56; 10,46</t>
+          <t>8,68; 10,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,9; 16,62</t>
+          <t>14,97; 16,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 14,94</t>
+          <t>13,56; 14,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 12,92</t>
+          <t>11,66; 12,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,22; 12,82</t>
+          <t>11,15; 12,76</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,72; 17,95</t>
+          <t>15,7; 18,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,6; 17,21</t>
+          <t>14,62; 17,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 15,83</t>
+          <t>13,87; 15,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,64</t>
+          <t>10,56; 13,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,12; 14,4</t>
+          <t>12,2; 14,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,44; 14,42</t>
+          <t>12,21; 14,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,54; 12,41</t>
+          <t>10,61; 12,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 10,18</t>
+          <t>8,53; 10,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,48; 16,2</t>
+          <t>14,58; 16,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,85; 15,78</t>
+          <t>13,91; 15,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,67; 14,13</t>
+          <t>12,68; 14,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,86; 11,84</t>
+          <t>9,91; 11,94</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,55; 17,42</t>
+          <t>15,69; 17,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 16,27</t>
+          <t>14,34; 16,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 13,98</t>
+          <t>12,14; 14,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,6; 15,23</t>
+          <t>12,74; 15,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,06; 15,04</t>
+          <t>13,01; 15,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,18; 14,29</t>
+          <t>12,13; 14,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,66; 12,53</t>
+          <t>10,58; 12,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 10,97</t>
+          <t>9,46; 11,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,83; 16,02</t>
+          <t>14,76; 16,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,64; 15,08</t>
+          <t>13,67; 15,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,63; 13,08</t>
+          <t>11,69; 13,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 12,97</t>
+          <t>11,45; 12,89</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,34; 17,36</t>
+          <t>16,3; 17,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,56; 16,67</t>
+          <t>15,56; 16,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,58; 14,64</t>
+          <t>13,61; 14,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,96; 14,33</t>
+          <t>12,89; 14,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,05; 13,19</t>
+          <t>12,1; 13,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,16</t>
+          <t>12,06; 13,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,46; 11,44</t>
+          <t>10,49; 11,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,18; 10,01</t>
+          <t>9,11; 10,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,87; 15,66</t>
+          <t>14,82; 15,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,22; 15,01</t>
+          <t>14,24; 15,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,35; 13,11</t>
+          <t>12,37; 13,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,39; 12,29</t>
+          <t>11,37; 12,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q24A01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q24A01-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,83</t>
+          <t>14,96</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,94</t>
+          <t>8,97</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,4</t>
+          <t>12,52</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,25; 17,23</t>
+          <t>15,24; 17,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,62; 19,47</t>
+          <t>16,58; 19,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,16; 16,35</t>
+          <t>14,05; 16,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,3; 16,31</t>
+          <t>13,51; 16,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,26; 11,32</t>
+          <t>9,32; 11,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,46; 12,94</t>
+          <t>10,56; 13,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 11,02</t>
+          <t>8,72; 11,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 9,82</t>
+          <t>8,15; 9,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,5; 15,04</t>
+          <t>13,45; 15,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,58; 16,63</t>
+          <t>14,56; 16,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,16; 13,93</t>
+          <t>12,13; 13,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,4; 13,36</t>
+          <t>11,63; 13,5</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>14,06</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,54</t>
+          <t>9,7</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,98</t>
+          <t>12,17</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,74; 18,9</t>
+          <t>16,65; 18,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,97; 16,98</t>
+          <t>15,01; 17,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,59; 14,62</t>
+          <t>12,58; 14,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,64; 15,05</t>
+          <t>12,86; 15,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 13,53</t>
+          <t>10,95; 13,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,06; 12,79</t>
+          <t>11,12; 12,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,97; 11,64</t>
+          <t>9,94; 11,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,68; 10,53</t>
+          <t>8,89; 10,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,97; 16,52</t>
+          <t>14,9; 16,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,56; 14,98</t>
+          <t>13,53; 14,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 12,98</t>
+          <t>11,68; 13,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,15; 12,76</t>
+          <t>11,37; 13,0</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,98</t>
+          <t>12,33</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,33</t>
+          <t>9,46</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,81</t>
+          <t>11,03</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,7; 18,0</t>
+          <t>15,71; 17,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14,62; 17,13</t>
+          <t>14,43; 17,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,87; 15,88</t>
+          <t>13,94; 15,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 13,65</t>
+          <t>10,75; 13,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,2; 14,42</t>
+          <t>12,12; 14,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,21; 14,38</t>
+          <t>12,39; 14,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,61; 12,42</t>
+          <t>10,52; 12,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 10,2</t>
+          <t>8,64; 10,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,58; 16,26</t>
+          <t>14,49; 16,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,91; 15,68</t>
+          <t>13,97; 15,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,68; 14,17</t>
+          <t>12,74; 14,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 11,94</t>
+          <t>10,22; 12,09</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,92</t>
+          <t>13,75</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,19</t>
+          <t>10,06</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,16</t>
+          <t>12,02</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,69; 17,53</t>
+          <t>15,62; 17,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,34; 16,06</t>
+          <t>14,43; 16,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,14; 14,09</t>
+          <t>12,15; 14,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,74; 15,28</t>
+          <t>12,65; 15,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,01; 15,01</t>
+          <t>12,98; 14,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,13; 14,26</t>
+          <t>12,2; 14,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,58; 12,45</t>
+          <t>10,54; 12,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 11,03</t>
+          <t>9,36; 10,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,76; 16,06</t>
+          <t>14,76; 16,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,67; 15,03</t>
+          <t>13,66; 15,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,69; 13,03</t>
+          <t>11,62; 12,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,45; 12,89</t>
+          <t>11,31; 12,71</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,64</t>
+          <t>13,77</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>9,61</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,84</t>
+          <t>11,93</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,3; 17,36</t>
+          <t>16,36; 17,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,56; 16,69</t>
+          <t>15,56; 16,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,61; 14,66</t>
+          <t>13,63; 14,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,89; 14,31</t>
+          <t>13,09; 14,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,1; 13,22</t>
+          <t>12,08; 13,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,1</t>
+          <t>12,04; 13,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,49; 11,44</t>
+          <t>10,53; 11,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,11; 10,02</t>
+          <t>9,21; 10,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,82; 15,64</t>
+          <t>14,88; 15,66</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,24; 15,05</t>
+          <t>14,22; 15,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,37; 13,13</t>
+          <t>12,35; 13,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,37; 12,27</t>
+          <t>11,52; 12,35</t>
         </is>
       </c>
     </row>
